--- a/PC_2009/AS_029.xlsx
+++ b/PC_2009/AS_029.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V229"/>
+  <dimension ref="A1:V231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -512,6 +590,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -520,7 +599,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Candidate_1</t>
+          <t>PS_Name</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -16239,89 +16318,254 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B229" s="7">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B229" s="9">
         <f>SUM(B6:B228)</f>
         <v/>
       </c>
-      <c r="C229" s="7">
+      <c r="C229" s="9">
         <f>SUM(C6:C228)</f>
         <v/>
       </c>
-      <c r="D229" s="7">
+      <c r="D229" s="9">
         <f>SUM(D6:D228)</f>
         <v/>
       </c>
-      <c r="E229" s="7">
+      <c r="E229" s="9">
         <f>SUM(E6:E228)</f>
         <v/>
       </c>
-      <c r="F229" s="7">
+      <c r="F229" s="9">
         <f>SUM(F6:F228)</f>
         <v/>
       </c>
-      <c r="G229" s="7">
+      <c r="G229" s="9">
         <f>SUM(G6:G228)</f>
         <v/>
       </c>
-      <c r="H229" s="7">
+      <c r="H229" s="9">
         <f>SUM(H6:H228)</f>
         <v/>
       </c>
-      <c r="I229" s="7">
+      <c r="I229" s="9">
         <f>SUM(I6:I228)</f>
         <v/>
       </c>
-      <c r="J229" s="7">
+      <c r="J229" s="9">
         <f>SUM(J6:J228)</f>
         <v/>
       </c>
-      <c r="K229" s="7">
+      <c r="K229" s="9">
         <f>SUM(K6:K228)</f>
         <v/>
       </c>
-      <c r="L229" s="7">
+      <c r="L229" s="9">
         <f>SUM(L6:L228)</f>
         <v/>
       </c>
-      <c r="M229" s="7">
+      <c r="M229" s="9">
         <f>SUM(M6:M228)</f>
         <v/>
       </c>
-      <c r="N229" s="7">
+      <c r="N229" s="9">
         <f>SUM(N6:N228)</f>
         <v/>
       </c>
-      <c r="O229" s="7">
+      <c r="O229" s="9">
         <f>SUM(O6:O228)</f>
         <v/>
       </c>
-      <c r="P229" s="7">
+      <c r="P229" s="9">
         <f>SUM(P6:P228)</f>
         <v/>
       </c>
-      <c r="Q229" s="7">
+      <c r="Q229" s="9">
         <f>SUM(Q6:Q228)</f>
         <v/>
       </c>
-      <c r="R229" s="7">
+      <c r="R229" s="9">
         <f>SUM(R6:R228)</f>
         <v/>
       </c>
-      <c r="S229" s="7">
+      <c r="S229" s="9">
         <f>SUM(S6:S228)</f>
         <v/>
       </c>
-      <c r="T229" s="7">
+      <c r="T229" s="9">
         <f>SUM(T6:T228)</f>
         <v/>
       </c>
-      <c r="U229" s="7">
+      <c r="U229" s="9">
         <f>SUM(U6:U228)</f>
+        <v/>
+      </c>
+      <c r="V229" s="9">
+        <f>SUM(V6:V228)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V230" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B231" s="13">
+        <f>B229+B230</f>
+        <v/>
+      </c>
+      <c r="C231" s="13">
+        <f>C229+C230</f>
+        <v/>
+      </c>
+      <c r="D231" s="13">
+        <f>D229+D230</f>
+        <v/>
+      </c>
+      <c r="E231" s="13">
+        <f>E229+E230</f>
+        <v/>
+      </c>
+      <c r="F231" s="13">
+        <f>F229+F230</f>
+        <v/>
+      </c>
+      <c r="G231" s="13">
+        <f>G229+G230</f>
+        <v/>
+      </c>
+      <c r="H231" s="13">
+        <f>H229+H230</f>
+        <v/>
+      </c>
+      <c r="I231" s="13">
+        <f>I229+I230</f>
+        <v/>
+      </c>
+      <c r="J231" s="13">
+        <f>J229+J230</f>
+        <v/>
+      </c>
+      <c r="K231" s="13">
+        <f>K229+K230</f>
+        <v/>
+      </c>
+      <c r="L231" s="13">
+        <f>L229+L230</f>
+        <v/>
+      </c>
+      <c r="M231" s="13">
+        <f>M229+M230</f>
+        <v/>
+      </c>
+      <c r="N231" s="13">
+        <f>N229+N230</f>
+        <v/>
+      </c>
+      <c r="O231" s="13">
+        <f>O229+O230</f>
+        <v/>
+      </c>
+      <c r="P231" s="13">
+        <f>P229+P230</f>
+        <v/>
+      </c>
+      <c r="Q231" s="13">
+        <f>Q229+Q230</f>
+        <v/>
+      </c>
+      <c r="R231" s="13">
+        <f>R229+R230</f>
+        <v/>
+      </c>
+      <c r="S231" s="13">
+        <f>S229+S230</f>
+        <v/>
+      </c>
+      <c r="T231" s="13">
+        <f>T229+T230</f>
+        <v/>
+      </c>
+      <c r="U231" s="13">
+        <f>U229+U230</f>
+        <v/>
+      </c>
+      <c r="V231" s="13">
+        <f>V229+V230</f>
         <v/>
       </c>
     </row>
